--- a/data/dividends_info_20260424.xlsx
+++ b/data/dividends_info_20260424.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.63999938964844</v>
+        <v>43.36999893188477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2062328168165564</v>
+        <v>0.2075167217351112</v>
       </c>
       <c r="J2" t="n">
         <v>325</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.09999847412109</v>
+        <v>55.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.27041745804906</v>
+        <v>1.261261261261261</v>
       </c>
       <c r="J3" t="n">
         <v>304</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.380000114440918</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6396588408098992</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J4" t="n">
         <v>234</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.63999938964844</v>
+        <v>43.36999893188477</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2062328168165564</v>
+        <v>0.2075167217351112</v>
       </c>
       <c r="J6" t="n">
         <v>234</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.940000057220459</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I8" t="n">
-        <v>3.367003334568775</v>
+        <v>3.338898291187508</v>
       </c>
       <c r="J8" t="n">
         <v>206</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.800000190734863</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I9" t="n">
-        <v>1.034482724601393</v>
+        <v>1.052631614170798</v>
       </c>
       <c r="J9" t="n">
         <v>178</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>43.63999938964844</v>
+        <v>43.36999893188477</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2062328168165564</v>
+        <v>0.2075167217351112</v>
       </c>
       <c r="J11" t="n">
         <v>150</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.139999866485596</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I13" t="n">
-        <v>4.071661326323361</v>
+        <v>4.159733618621054</v>
       </c>
       <c r="J13" t="n">
         <v>94</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.777000427246094</v>
+        <v>9.821000099182129</v>
       </c>
       <c r="I14" t="n">
-        <v>2.659302328303515</v>
+        <v>2.647388222933143</v>
       </c>
       <c r="J14" t="n">
         <v>87</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.71999931335449</v>
+        <v>16.3799991607666</v>
       </c>
       <c r="I15" t="n">
-        <v>3.588516893782237</v>
+        <v>3.663003850678582</v>
       </c>
       <c r="J15" t="n">
         <v>87</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.782000064849854</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="I16" t="n">
-        <v>5.817027927754255</v>
+        <v>5.789473756858848</v>
       </c>
       <c r="J16" t="n">
         <v>87</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.925000190734863</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I18" t="n">
-        <v>1.687763658748461</v>
+        <v>1.692047421012851</v>
       </c>
       <c r="J18" t="n">
         <v>87</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.690000057220459</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="I20" t="n">
-        <v>2.108963071937463</v>
+        <v>2.173913050989873</v>
       </c>
       <c r="J20" t="n">
         <v>80</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.489999771118164</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="I23" t="n">
-        <v>1.559020124015899</v>
+        <v>1.627906904535209</v>
       </c>
       <c r="J23" t="n">
         <v>73</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>33.95000076293945</v>
+        <v>34.15000152587891</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4418262050931769</v>
+        <v>0.43923863337555</v>
       </c>
       <c r="J24" t="n">
         <v>73</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.099999904632568</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6557377151698397</v>
+        <v>0.6249999906867744</v>
       </c>
       <c r="J25" t="n">
         <v>66</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22.45999908447266</v>
+        <v>22.44000053405762</v>
       </c>
       <c r="I26" t="n">
-        <v>1.113089983039373</v>
+        <v>1.114081969920501</v>
       </c>
       <c r="J26" t="n">
         <v>59</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26.25</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7558139758387714</v>
       </c>
       <c r="J27" t="n">
         <v>59</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1.970000028610229</v>
       </c>
       <c r="I28" t="n">
-        <v>1.65</v>
+        <v>1.675126879225501</v>
       </c>
       <c r="J28" t="n">
         <v>59</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.039999961853027</v>
+        <v>5.045000076293945</v>
       </c>
       <c r="I29" t="n">
-        <v>5.75396829751914</v>
+        <v>5.748265522585163</v>
       </c>
       <c r="J29" t="n">
         <v>59</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.104000091552734</v>
+        <v>4.087999820709229</v>
       </c>
       <c r="I30" t="n">
-        <v>3.898635390611421</v>
+        <v>3.913894496508113</v>
       </c>
       <c r="J30" t="n">
         <v>59</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.575999975204468</v>
+        <v>2.604000091552734</v>
       </c>
       <c r="I31" t="n">
-        <v>5.380434834398582</v>
+        <v>5.322580458027345</v>
       </c>
       <c r="J31" t="n">
         <v>59</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>53.34999847412109</v>
+        <v>52.70000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>1.18088100847013</v>
+        <v>1.1954459029971</v>
       </c>
       <c r="J32" t="n">
         <v>59</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.144999980926514</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I33" t="n">
-        <v>2.721088445461739</v>
+        <v>2.734375061118046</v>
       </c>
       <c r="J33" t="n">
         <v>59</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18.70000076293945</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I34" t="n">
-        <v>4.171122824475178</v>
+        <v>4.06249983857076</v>
       </c>
       <c r="J34" t="n">
         <v>59</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>21.98999977111816</v>
+        <v>22.29000091552734</v>
       </c>
       <c r="I35" t="n">
-        <v>3.865393400851221</v>
+        <v>3.813369067238956</v>
       </c>
       <c r="J35" t="n">
         <v>59</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>43.63999938964844</v>
+        <v>43.36999893188477</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2062328168165564</v>
+        <v>0.2075167217351112</v>
       </c>
       <c r="J36" t="n">
         <v>59</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6.722000122070312</v>
+        <v>6.684000015258789</v>
       </c>
       <c r="I37" t="n">
-        <v>2.697113905201199</v>
+        <v>2.71244762995382</v>
       </c>
       <c r="J37" t="n">
         <v>59</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8.329999923706055</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I38" t="n">
-        <v>3.121248527987079</v>
+        <v>3.095238235802344</v>
       </c>
       <c r="J38" t="n">
         <v>59</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10.1899995803833</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="I39" t="n">
-        <v>2.718351436767974</v>
+        <v>2.715686325291771</v>
       </c>
       <c r="J39" t="n">
         <v>59</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.195000052452087</v>
+        <v>1.179999947547913</v>
       </c>
       <c r="I40" t="n">
-        <v>1.129707063384524</v>
+        <v>1.14406784746504</v>
       </c>
       <c r="J40" t="n">
         <v>52</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.015999794006348</v>
+        <v>3.983999967575073</v>
       </c>
       <c r="I41" t="n">
-        <v>2.739043965195635</v>
+        <v>2.761044199178377</v>
       </c>
       <c r="J41" t="n">
         <v>52</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.35000038146973</v>
+        <v>28.29999923706055</v>
       </c>
       <c r="I43" t="n">
-        <v>3.915343862660136</v>
+        <v>3.922261589839156</v>
       </c>
       <c r="J43" t="n">
         <v>41</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9269999861717224</v>
+        <v>0.9350000023841858</v>
       </c>
       <c r="I44" t="n">
-        <v>3.236246002968401</v>
+        <v>3.208556141551022</v>
       </c>
       <c r="J44" t="n">
         <v>38</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.5210000276565552</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I45" t="n">
-        <v>4.41458709771157</v>
+        <v>4.509804005899691</v>
       </c>
       <c r="J45" t="n">
         <v>38</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.625</v>
+        <v>2.589999914169312</v>
       </c>
       <c r="I48" t="n">
-        <v>6.857142857142858</v>
+        <v>6.949807180118431</v>
       </c>
       <c r="J48" t="n">
         <v>31</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13.05000019073486</v>
+        <v>13</v>
       </c>
       <c r="I50" t="n">
-        <v>1.915708784261115</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="J50" t="n">
         <v>31</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.349999904632568</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8955224135533352</v>
+        <v>0.909090922226919</v>
       </c>
       <c r="J51" t="n">
         <v>31</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.779999971389771</v>
+        <v>3.730000019073486</v>
       </c>
       <c r="I52" t="n">
-        <v>3.968253998289063</v>
+        <v>4.02144770061581</v>
       </c>
       <c r="J52" t="n">
         <v>31</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>13.60000038146973</v>
+        <v>13.55000019073486</v>
       </c>
       <c r="I53" t="n">
-        <v>4.264705762731166</v>
+        <v>4.280442744174932</v>
       </c>
       <c r="J53" t="n">
         <v>31</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2.394999980926514</v>
+        <v>2.391000032424927</v>
       </c>
       <c r="I54" t="n">
-        <v>4.342379992828528</v>
+        <v>4.349644441222542</v>
       </c>
       <c r="J54" t="n">
         <v>24</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9.539999961853027</v>
+        <v>9.522000312805176</v>
       </c>
       <c r="I55" t="n">
-        <v>3.039832297270482</v>
+        <v>3.045578559895743</v>
       </c>
       <c r="J55" t="n">
         <v>24</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>37.41999816894531</v>
+        <v>37.88999938964844</v>
       </c>
       <c r="I57" t="n">
-        <v>4.382683271644381</v>
+        <v>4.328318887352763</v>
       </c>
       <c r="J57" t="n">
         <v>24</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>36.79999923706055</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="I58" t="n">
-        <v>5.434782721369841</v>
+        <v>5.385029706159432</v>
       </c>
       <c r="J58" t="n">
         <v>24</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.986000061035156</v>
+        <v>3.940000057220459</v>
       </c>
       <c r="I59" t="n">
-        <v>2.508780694148565</v>
+        <v>2.538071029129546</v>
       </c>
       <c r="J59" t="n">
         <v>24</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>33.7599983215332</v>
+        <v>32.45000076293945</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4397512066975059</v>
+        <v>0.4575038413236447</v>
       </c>
       <c r="J60" t="n">
         <v>24</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>22.65999984741211</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="I61" t="n">
-        <v>4.060017679590007</v>
+        <v>4.028020988851698</v>
       </c>
       <c r="J61" t="n">
         <v>24</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>8.289999961853027</v>
+        <v>8.274999618530273</v>
       </c>
       <c r="I62" t="n">
-        <v>3.618817869486965</v>
+        <v>3.625377810631043</v>
       </c>
       <c r="J62" t="n">
         <v>24</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>82.86000061035156</v>
+        <v>83.90000152587891</v>
       </c>
       <c r="I63" t="n">
-        <v>1.255129124232802</v>
+        <v>1.239570895215315</v>
       </c>
       <c r="J63" t="n">
         <v>24</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>46.72000122070312</v>
+        <v>46.7599983215332</v>
       </c>
       <c r="I64" t="n">
-        <v>1.498287632085522</v>
+        <v>1.497006041759515</v>
       </c>
       <c r="J64" t="n">
         <v>24</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>55.09999847412109</v>
+        <v>55.5</v>
       </c>
       <c r="I65" t="n">
-        <v>3.992740582439903</v>
+        <v>3.963963963963964</v>
       </c>
       <c r="J65" t="n">
         <v>24</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>8.953000068664551</v>
+        <v>8.991000175476074</v>
       </c>
       <c r="I66" t="n">
-        <v>9.605718679819908</v>
+        <v>9.565120489550685</v>
       </c>
       <c r="J66" t="n">
         <v>24</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>11.86200046539307</v>
+        <v>11.96399974822998</v>
       </c>
       <c r="I67" t="n">
-        <v>4.720957494764721</v>
+        <v>4.680708891546487</v>
       </c>
       <c r="J67" t="n">
         <v>24</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2.200000047683716</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I68" t="n">
-        <v>1.81818177877379</v>
+        <v>1.826483970542351</v>
       </c>
       <c r="J68" t="n">
         <v>24</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>9.640000343322754</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="I69" t="n">
-        <v>3.112033084187576</v>
+        <v>3.174603238678043</v>
       </c>
       <c r="J69" t="n">
         <v>24</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>2.279999971389771</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I70" t="n">
-        <v>4.736842164702693</v>
+        <v>4.821428550901461</v>
       </c>
       <c r="J70" t="n">
         <v>24</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>73.19999694824219</v>
+        <v>73</v>
       </c>
       <c r="I71" t="n">
-        <v>2.814207767599461</v>
+        <v>2.821917808219178</v>
       </c>
       <c r="J71" t="n">
         <v>24</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>15.10999965667725</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I72" t="n">
-        <v>4.963600377506086</v>
+        <v>4.95376474896036</v>
       </c>
       <c r="J72" t="n">
         <v>24</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>15.39000034332275</v>
+        <v>15.9399995803833</v>
       </c>
       <c r="I73" t="n">
-        <v>1.94931769530571</v>
+        <v>1.882057765981359</v>
       </c>
       <c r="J73" t="n">
         <v>24</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>44.59999847412109</v>
+        <v>45.29999923706055</v>
       </c>
       <c r="I74" t="n">
-        <v>1.905829661615813</v>
+        <v>1.876379722551084</v>
       </c>
       <c r="J74" t="n">
         <v>24</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>33.31999969482422</v>
+        <v>33.36000061035156</v>
       </c>
       <c r="I75" t="n">
-        <v>2.551020431527901</v>
+        <v>2.547961584078168</v>
       </c>
       <c r="J75" t="n">
         <v>24</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>59.86000061035156</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="I76" t="n">
-        <v>2.171734023963895</v>
+        <v>2.173913071213446</v>
       </c>
       <c r="J76" t="n">
         <v>24</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>8.100000381469727</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="I77" t="n">
-        <v>7.407407058555364</v>
+        <v>7.334963051533854</v>
       </c>
       <c r="J77" t="n">
         <v>24</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>6.150000095367432</v>
+        <v>6</v>
       </c>
       <c r="I78" t="n">
-        <v>7.642276304256217</v>
+        <v>7.833333333333332</v>
       </c>
       <c r="J78" t="n">
         <v>24</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>5.940000057220459</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I79" t="n">
-        <v>3.367003334568775</v>
+        <v>3.338898291187508</v>
       </c>
       <c r="J79" t="n">
         <v>24</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>22.6200008392334</v>
+        <v>22.57999992370605</v>
       </c>
       <c r="I80" t="n">
-        <v>4.42086632581173</v>
+        <v>4.428697977762748</v>
       </c>
       <c r="J80" t="n">
         <v>24</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>4.880000114440918</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="I81" t="n">
-        <v>4.405737601599046</v>
+        <v>4.574468270746932</v>
       </c>
       <c r="J81" t="n">
         <v>24</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>23.45999908447266</v>
+        <v>22.95000076293945</v>
       </c>
       <c r="I82" t="n">
-        <v>1.150895185578688</v>
+        <v>1.176470549125238</v>
       </c>
       <c r="J82" t="n">
         <v>24</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>8.199999809265137</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="I83" t="n">
-        <v>2.439024446976463</v>
+        <v>2.444987683844618</v>
       </c>
       <c r="J83" t="n">
         <v>24</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>9.375</v>
+        <v>9.310000419616699</v>
       </c>
       <c r="I84" t="n">
-        <v>2.56</v>
+        <v>2.577873138376088</v>
       </c>
       <c r="J84" t="n">
         <v>24</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>21.09000015258789</v>
+        <v>20.94000053405762</v>
       </c>
       <c r="I85" t="n">
-        <v>3.745851087170625</v>
+        <v>3.772683762424522</v>
       </c>
       <c r="J85" t="n">
         <v>24</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.909999847412109</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I86" t="n">
-        <v>1.894093745217061</v>
+        <v>1.886409801992638</v>
       </c>
       <c r="J86" t="n">
         <v>24</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.800000190734863</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I87" t="n">
-        <v>1.034482724601393</v>
+        <v>1.052631614170798</v>
       </c>
       <c r="J87" t="n">
         <v>24</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>35.77999877929688</v>
+        <v>36.13999938964844</v>
       </c>
       <c r="I88" t="n">
-        <v>0.978200145167467</v>
+        <v>0.9684560207830283</v>
       </c>
       <c r="J88" t="n">
         <v>24</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>7.329999923706055</v>
+        <v>7.255000114440918</v>
       </c>
       <c r="I89" t="n">
-        <v>7.562073748559406</v>
+        <v>7.640247984237493</v>
       </c>
       <c r="J89" t="n">
         <v>24</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>2.240000009536743</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I90" t="n">
-        <v>2.678571417167479</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J90" t="n">
         <v>24</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>12.85000038146973</v>
+        <v>12.75</v>
       </c>
       <c r="I91" t="n">
-        <v>1.556420187258585</v>
+        <v>1.568627450980392</v>
       </c>
       <c r="J91" t="n">
         <v>24</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6.159999847412109</v>
+        <v>6.125</v>
       </c>
       <c r="I92" t="n">
-        <v>1.672077963496567</v>
+        <v>1.681632653061224</v>
       </c>
       <c r="J92" t="n">
         <v>24</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5.591000080108643</v>
+        <v>5.658999919891357</v>
       </c>
       <c r="I93" t="n">
-        <v>3.39831867783318</v>
+        <v>3.357483701884337</v>
       </c>
       <c r="J93" t="n">
         <v>24</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>10.35999965667725</v>
+        <v>10.30500030517578</v>
       </c>
       <c r="I94" t="n">
-        <v>4.169884308071058</v>
+        <v>4.192139613843816</v>
       </c>
       <c r="J94" t="n">
         <v>24</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>25.93000030517578</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="I95" t="n">
-        <v>1.696876185196856</v>
+        <v>1.685823730149781</v>
       </c>
       <c r="J95" t="n">
         <v>24</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>53.02000045776367</v>
+        <v>54.09999847412109</v>
       </c>
       <c r="I98" t="n">
-        <v>2.640512991159357</v>
+        <v>2.587800442674124</v>
       </c>
       <c r="J98" t="n">
         <v>24</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3.779000043869019</v>
+        <v>3.813999891281128</v>
       </c>
       <c r="I99" t="n">
-        <v>7.938608005223884</v>
+        <v>7.865757958876856</v>
       </c>
       <c r="J99" t="n">
         <v>24</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>12.19999980926514</v>
+        <v>12.25</v>
       </c>
       <c r="I100" t="n">
-        <v>0.9836065727547595</v>
+        <v>0.9795918367346939</v>
       </c>
       <c r="J100" t="n">
         <v>24</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3.509999990463257</v>
+        <v>3.5</v>
       </c>
       <c r="I101" t="n">
-        <v>4.843304856464204</v>
+        <v>4.857142857142858</v>
       </c>
       <c r="J101" t="n">
         <v>24</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>20.75</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="I102" t="n">
-        <v>3.373493975903615</v>
+        <v>3.381642387440174</v>
       </c>
       <c r="J102" t="n">
         <v>24</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>6.199999809265137</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="I104" t="n">
-        <v>5.322580808903504</v>
+        <v>5.339805973566092</v>
       </c>
       <c r="J104" t="n">
         <v>24</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9800000190734863</v>
+        <v>0.9929999709129333</v>
       </c>
       <c r="I105" t="n">
-        <v>7.142857003837566</v>
+        <v>7.049345624415697</v>
       </c>
       <c r="J105" t="n">
         <v>24</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>49.91999816894531</v>
+        <v>49.5</v>
       </c>
       <c r="I106" t="n">
-        <v>1.422275693194403</v>
+        <v>1.434343434343434</v>
       </c>
       <c r="J106" t="n">
         <v>24</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>91.05000305175781</v>
+        <v>91.69999694824219</v>
       </c>
       <c r="I107" t="n">
-        <v>1.48270176249482</v>
+        <v>1.472191979201455</v>
       </c>
       <c r="J107" t="n">
         <v>24</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7.099999904632568</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I108" t="n">
-        <v>1.126760578514967</v>
+        <v>1.111111140545505</v>
       </c>
       <c r="J108" t="n">
         <v>24</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>4.327000141143799</v>
+        <v>4.336999893188477</v>
       </c>
       <c r="I110" t="n">
-        <v>3.928818915061607</v>
+        <v>3.919760299440989</v>
       </c>
       <c r="J110" t="n">
         <v>24</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>59.09999847412109</v>
+        <v>59.29999923706055</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7614213394557828</v>
+        <v>0.7588532981274725</v>
       </c>
       <c r="J112" t="n">
         <v>24</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>4.739999771118164</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8438818972888689</v>
+        <v>0.8602150361211831</v>
       </c>
       <c r="J113" t="n">
         <v>24</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>19.76000022888184</v>
+        <v>19.79000091552734</v>
       </c>
       <c r="I116" t="n">
-        <v>1.923076900801753</v>
+        <v>1.92016160899644</v>
       </c>
       <c r="J116" t="n">
         <v>24</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>26.95000076293945</v>
+        <v>26.78000068664551</v>
       </c>
       <c r="I117" t="n">
-        <v>2.226345020461356</v>
+        <v>2.240477911186927</v>
       </c>
       <c r="J117" t="n">
         <v>24</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>35.65000152587891</v>
+        <v>35.70000076293945</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9817671389044105</v>
+        <v>0.9803921359109288</v>
       </c>
       <c r="J118" t="n">
         <v>24</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.480000019073486</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="I119" t="n">
-        <v>0.488505744448992</v>
+        <v>0.4999999859753781</v>
       </c>
       <c r="J119" t="n">
         <v>24</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2.910000085830688</v>
+        <v>2.924999952316284</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3436426015480821</v>
+        <v>0.341880347453718</v>
       </c>
       <c r="J120" t="n">
         <v>24</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>21.95000076293945</v>
+        <v>22.15999984741211</v>
       </c>
       <c r="I121" t="n">
-        <v>5.102505517407619</v>
+        <v>5.054151659350286</v>
       </c>
       <c r="J121" t="n">
         <v>24</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>2.513999938964844</v>
+        <v>2.46399998664856</v>
       </c>
       <c r="I123" t="n">
-        <v>3.221957118795806</v>
+        <v>3.287337680150443</v>
       </c>
       <c r="J123" t="n">
         <v>24</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.398000001907349</v>
+        <v>2.394000053405762</v>
       </c>
       <c r="I124" t="n">
-        <v>3.849040864327997</v>
+        <v>3.855471927358222</v>
       </c>
       <c r="J124" t="n">
         <v>24</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9.319999694824219</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I125" t="n">
-        <v>3.755364929833307</v>
+        <v>3.796095334743296</v>
       </c>
       <c r="J125" t="n">
         <v>17</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>5.550000190734863</v>
+        <v>5.25</v>
       </c>
       <c r="I126" t="n">
-        <v>1.729729670284729</v>
+        <v>1.828571428571429</v>
       </c>
       <c r="J126" t="n">
         <v>17</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>6</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>4.878048704844394</v>
       </c>
       <c r="J127" t="n">
         <v>17</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>11.89999961853027</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>1.680672322783665</v>
+        <v>1.724137874335655</v>
       </c>
       <c r="J128" t="n">
         <v>17</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.380000114440918</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6396588408098992</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J129" t="n">
         <v>17</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>16.07999992370605</v>
+        <v>15.92000007629395</v>
       </c>
       <c r="I131" t="n">
-        <v>3.109452751071668</v>
+        <v>3.140703502536642</v>
       </c>
       <c r="J131" t="n">
         <v>17</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>4.019999980926514</v>
+        <v>4</v>
       </c>
       <c r="I132" t="n">
-        <v>2.487562200857334</v>
+        <v>2.5</v>
       </c>
       <c r="J132" t="n">
         <v>17</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2.950000047683716</v>
+        <v>3</v>
       </c>
       <c r="I133" t="n">
-        <v>3.728813499049599</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="J133" t="n">
         <v>17</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.350000381469727</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9090908720010005</v>
+        <v>0.880829050363691</v>
       </c>
       <c r="J134" t="n">
         <v>17</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>4.860000133514404</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I135" t="n">
-        <v>1.954732456587461</v>
+        <v>1.946721265822835</v>
       </c>
       <c r="J135" t="n">
         <v>17</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>7.849999904632568</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="I137" t="n">
-        <v>1.14649682921509</v>
+        <v>1.1392404925764</v>
       </c>
       <c r="J137" t="n">
         <v>17</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>7.010000228881836</v>
+        <v>7.070000171661377</v>
       </c>
       <c r="I139" t="n">
-        <v>3.138373649312878</v>
+        <v>3.11173966984929</v>
       </c>
       <c r="J139" t="n">
         <v>17</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>3.404999971389771</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="I140" t="n">
-        <v>4.69897213933588</v>
+        <v>4.733727650375108</v>
       </c>
       <c r="J140" t="n">
         <v>10</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>23.85000038146973</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="I141" t="n">
-        <v>2.557651950705795</v>
+        <v>2.474645068722197</v>
       </c>
       <c r="J141" t="n">
         <v>10</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.130000114440918</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I142" t="n">
-        <v>4.792332093150517</v>
+        <v>4.950495096249109</v>
       </c>
       <c r="J142" t="n">
         <v>10</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>12.5</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="I143" t="n">
-        <v>5.6</v>
+        <v>5.69105682231846</v>
       </c>
       <c r="J143" t="n">
         <v>10</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>9.149999618530273</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="I144" t="n">
-        <v>5.579235205279708</v>
+        <v>5.567066474947277</v>
       </c>
       <c r="J144" t="n">
         <v>10</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>7.724999904632568</v>
+        <v>7.690000057220459</v>
       </c>
       <c r="I145" t="n">
-        <v>3.495145674216579</v>
+        <v>3.511053289869431</v>
       </c>
       <c r="J145" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>5.880000114440918</v>
+        <v>5.775000095367432</v>
       </c>
       <c r="I146" t="n">
-        <v>5.952380836531304</v>
+        <v>6.060605960522177</v>
       </c>
       <c r="J146" t="n">
         <v>10</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>18.79999923706055</v>
+        <v>18.75</v>
       </c>
       <c r="I148" t="n">
-        <v>3.989361864023487</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
         <v>10</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>11.14999961853027</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I149" t="n">
-        <v>3.856502374093175</v>
+        <v>3.771929950778691</v>
       </c>
       <c r="J149" t="n">
         <v>10</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>4.369999885559082</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I150" t="n">
-        <v>3.43249436906586</v>
+        <v>3.521126571379833</v>
       </c>
       <c r="J150" t="n">
         <v>10</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>12.38000011444092</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="I151" t="n">
-        <v>1.592641342305062</v>
+        <v>1.590072629561659</v>
       </c>
       <c r="J151" t="n">
         <v>10</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>29.04999923706055</v>
+        <v>28.95000076293945</v>
       </c>
       <c r="I152" t="n">
-        <v>3.786574970358948</v>
+        <v>3.799654476721717</v>
       </c>
       <c r="J152" t="n">
         <v>10</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>79.69999694824219</v>
+        <v>79.80000305175781</v>
       </c>
       <c r="I154" t="n">
-        <v>1.505646230801351</v>
+        <v>1.503759340988605</v>
       </c>
       <c r="J154" t="n">
         <v>10</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>24.45000076293945</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="I155" t="n">
-        <v>1.104294444069129</v>
+        <v>1.115702444164735</v>
       </c>
       <c r="J155" t="n">
         <v>10</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>29.95000076293945</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I157" t="n">
-        <v>1.001669423565505</v>
+        <v>0.9900990348312084</v>
       </c>
       <c r="J157" t="n">
         <v>10</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.1909999996423721</v>
       </c>
       <c r="I158" t="n">
-        <v>3.575076492117605</v>
+        <v>3.664921472830776</v>
       </c>
       <c r="J158" t="n">
         <v>3</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>7.5</v>
+        <v>7.539999961853027</v>
       </c>
       <c r="I159" t="n">
-        <v>2.133333333333333</v>
+        <v>2.122015925855237</v>
       </c>
       <c r="J159" t="n">
         <v>3</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>8.279999732971191</v>
+        <v>7.980000019073486</v>
       </c>
       <c r="I161" t="n">
-        <v>3.019323768870342</v>
+        <v>3.132832072712528</v>
       </c>
       <c r="J161" t="n">
         <v>3</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>1.509999990463257</v>
+        <v>1.5</v>
       </c>
       <c r="I162" t="n">
-        <v>4.635761618682165</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="J162" t="n">
         <v>3</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>6.420000076293945</v>
+        <v>6.5</v>
       </c>
       <c r="I163" t="n">
-        <v>7.788161901216574</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="J163" t="n">
         <v>-4</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>18.16500091552734</v>
+        <v>18.28499984741211</v>
       </c>
       <c r="I164" t="n">
-        <v>3.578309756342393</v>
+        <v>3.554826390069645</v>
       </c>
       <c r="J164" t="n">
         <v>-4</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>12.10999965667725</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="I165" t="n">
-        <v>4.459124816756319</v>
+        <v>4.433497425862394</v>
       </c>
       <c r="J165" t="n">
         <v>-4</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.177999973297119</v>
+        <v>6.228000164031982</v>
       </c>
       <c r="I166" t="n">
-        <v>1.618646818261984</v>
+        <v>1.605651852379856</v>
       </c>
       <c r="J166" t="n">
         <v>-4</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>9.300000190734863</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I167" t="n">
-        <v>1.720430072242366</v>
+        <v>1.746724919926754</v>
       </c>
       <c r="J167" t="n">
         <v>-4</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>299.2000122070312</v>
+        <v>299.5499877929688</v>
       </c>
       <c r="I168" t="n">
-        <v>1.208221875839565</v>
+        <v>1.206810264501988</v>
       </c>
       <c r="J168" t="n">
         <v>-4</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>29.10000038146973</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I169" t="n">
-        <v>4.673539457635265</v>
+        <v>4.64163834611908</v>
       </c>
       <c r="J169" t="n">
         <v>-4</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>14.71000003814697</v>
+        <v>14.6899995803833</v>
       </c>
       <c r="I171" t="n">
-        <v>3.976886461474766</v>
+        <v>3.982300998709326</v>
       </c>
       <c r="J171" t="n">
         <v>-4</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>19.63500022888184</v>
+        <v>19.65500068664551</v>
       </c>
       <c r="I172" t="n">
-        <v>3.20855611233103</v>
+        <v>3.20529116250833</v>
       </c>
       <c r="J172" t="n">
         <v>-4</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>123.6999969482422</v>
+        <v>127.4000015258789</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7275667115631156</v>
+        <v>0.7064364122610957</v>
       </c>
       <c r="J173" t="n">
         <v>-4</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>63.33000183105469</v>
+        <v>64.01000213623047</v>
       </c>
       <c r="I174" t="n">
-        <v>2.717195563313854</v>
+        <v>2.688329858726884</v>
       </c>
       <c r="J174" t="n">
         <v>-4</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>26.5</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5447470655405048</v>
       </c>
       <c r="J175" t="n">
         <v>-11</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1.590000033378601</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="I176" t="n">
-        <v>3.773584826442149</v>
+        <v>3.797468251285027</v>
       </c>
       <c r="J176" t="n">
         <v>-11</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>2.160000085830688</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I177" t="n">
-        <v>1.574074011525993</v>
+        <v>1.588784968845712</v>
       </c>
       <c r="J177" t="n">
         <v>-25</v>
@@ -9627,7 +9627,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9644,7 +9644,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9661,7 +9661,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9678,7 +9678,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9688,14 +9688,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9712,7 +9712,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9729,7 +9729,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9824,14 +9824,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9841,14 +9841,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9882,7 +9882,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9899,7 +9899,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9916,7 +9916,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9943,14 +9943,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9967,7 +9967,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9984,7 +9984,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10001,7 +10001,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10035,7 +10035,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10069,7 +10069,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10137,7 +10137,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10171,7 +10171,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10188,7 +10188,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10205,7 +10205,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10222,7 +10222,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10307,7 +10307,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10341,7 +10341,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10375,7 +10375,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10392,7 +10392,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10409,7 +10409,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10426,7 +10426,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10443,7 +10443,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10460,7 +10460,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10470,14 +10470,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10494,7 +10494,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10511,7 +10511,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10528,7 +10528,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10545,7 +10545,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10562,7 +10562,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10579,7 +10579,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10596,7 +10596,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10613,7 +10613,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10630,7 +10630,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10640,14 +10640,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10664,7 +10664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10681,7 +10681,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10698,7 +10698,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10715,7 +10715,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10732,7 +10732,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10749,7 +10749,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10766,7 +10766,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10783,7 +10783,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10800,7 +10800,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10810,14 +10810,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10851,7 +10851,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10902,7 +10902,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10919,7 +10919,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10953,7 +10953,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10970,7 +10970,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10987,7 +10987,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11004,7 +11004,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11014,14 +11014,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11038,7 +11038,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11055,7 +11055,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11072,7 +11072,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11089,7 +11089,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11099,14 +11099,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11116,14 +11116,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11140,7 +11140,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11157,7 +11157,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11167,14 +11167,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11191,7 +11191,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11201,14 +11201,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11218,14 +11218,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11242,7 +11242,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11259,7 +11259,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11276,7 +11276,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11293,7 +11293,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11303,14 +11303,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11327,7 +11327,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11344,7 +11344,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11361,7 +11361,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11378,7 +11378,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11412,7 +11412,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11429,7 +11429,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11463,7 +11463,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11473,14 +11473,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11490,14 +11490,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11514,7 +11514,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11524,14 +11524,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11541,14 +11541,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11565,7 +11565,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11599,7 +11599,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11616,7 +11616,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11633,7 +11633,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11650,7 +11650,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11677,14 +11677,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11701,7 +11701,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11718,7 +11718,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11735,7 +11735,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11752,7 +11752,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11769,7 +11769,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11786,7 +11786,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11803,7 +11803,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11813,14 +11813,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11830,14 +11830,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11871,7 +11871,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11888,7 +11888,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11898,14 +11898,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11922,7 +11922,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11939,7 +11939,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11956,7 +11956,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11973,7 +11973,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11983,14 +11983,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12007,7 +12007,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12024,7 +12024,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12041,7 +12041,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12051,14 +12051,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12075,7 +12075,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12109,7 +12109,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12126,7 +12126,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12143,7 +12143,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12160,7 +12160,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12177,7 +12177,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12194,7 +12194,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12211,7 +12211,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12221,14 +12221,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12245,7 +12245,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12255,14 +12255,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12272,14 +12272,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12289,14 +12289,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12313,7 +12313,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12330,7 +12330,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12374,14 +12374,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12398,7 +12398,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12415,7 +12415,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12425,14 +12425,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12442,14 +12442,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12459,14 +12459,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12483,7 +12483,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12500,7 +12500,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12517,7 +12517,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12534,7 +12534,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12551,7 +12551,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12568,7 +12568,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12585,7 +12585,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12602,7 +12602,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12619,7 +12619,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12636,7 +12636,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12653,7 +12653,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12670,7 +12670,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12687,7 +12687,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12704,7 +12704,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12721,7 +12721,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12738,7 +12738,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12748,14 +12748,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12772,7 +12772,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12789,7 +12789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12823,7 +12823,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12840,7 +12840,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12857,7 +12857,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12874,7 +12874,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12891,7 +12891,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12901,14 +12901,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12925,7 +12925,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12942,7 +12942,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12959,7 +12959,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12976,7 +12976,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12993,7 +12993,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13027,7 +13027,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13044,7 +13044,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13061,7 +13061,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13071,14 +13071,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13095,7 +13095,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13112,7 +13112,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13122,14 +13122,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13146,7 +13146,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13163,7 +13163,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13180,7 +13180,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13190,14 +13190,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13231,7 +13231,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13248,7 +13248,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13265,7 +13265,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13282,7 +13282,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13299,7 +13299,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13309,14 +13309,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13333,7 +13333,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13350,7 +13350,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13367,7 +13367,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13384,7 +13384,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13401,7 +13401,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13418,7 +13418,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13428,14 +13428,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13445,14 +13445,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13503,7 +13503,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13520,7 +13520,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13530,14 +13530,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13547,14 +13547,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13571,7 +13571,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13588,7 +13588,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13605,7 +13605,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13615,14 +13615,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13632,14 +13632,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13656,7 +13656,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13673,7 +13673,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13683,14 +13683,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13707,7 +13707,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13741,7 +13741,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13758,7 +13758,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13768,14 +13768,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13785,14 +13785,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13802,14 +13802,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13826,7 +13826,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13843,7 +13843,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13860,7 +13860,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13870,14 +13870,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13911,7 +13911,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13921,14 +13921,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13945,7 +13945,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13955,14 +13955,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13972,14 +13972,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13989,14 +13989,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14006,14 +14006,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14023,14 +14023,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14040,14 +14040,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14057,14 +14057,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14081,7 +14081,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14091,14 +14091,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14115,7 +14115,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14132,7 +14132,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14142,14 +14142,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14159,14 +14159,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14183,7 +14183,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14193,14 +14193,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14210,14 +14210,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14227,14 +14227,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14244,14 +14244,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14268,7 +14268,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14295,14 +14295,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14319,7 +14319,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14329,14 +14329,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14346,14 +14346,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14370,7 +14370,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14380,14 +14380,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14404,7 +14404,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14414,14 +14414,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14431,14 +14431,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14448,14 +14448,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14465,14 +14465,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14482,14 +14482,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14506,7 +14506,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14516,14 +14516,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14533,14 +14533,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14584,14 +14584,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14601,14 +14601,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -14635,14 +14635,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14652,14 +14652,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14669,14 +14669,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14693,7 +14693,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14710,7 +14710,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14720,14 +14720,14 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14737,14 +14737,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14754,14 +14754,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14771,14 +14771,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14795,7 +14795,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14812,7 +14812,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14822,14 +14822,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14846,7 +14846,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14863,7 +14863,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14873,14 +14873,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14897,7 +14897,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14914,7 +14914,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14931,7 +14931,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14941,14 +14941,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14958,14 +14958,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14975,14 +14975,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14992,14 +14992,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15009,14 +15009,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15033,7 +15033,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15043,14 +15043,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15084,7 +15084,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15101,7 +15101,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15111,14 +15111,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15128,14 +15128,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15145,14 +15145,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15169,7 +15169,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15179,14 +15179,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15196,14 +15196,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15213,14 +15213,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15230,14 +15230,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15247,14 +15247,14 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15271,7 +15271,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15281,14 +15281,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15298,14 +15298,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15315,14 +15315,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15339,7 +15339,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15356,7 +15356,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15366,14 +15366,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -15424,7 +15424,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15441,7 +15441,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15468,14 +15468,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15502,14 +15502,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15519,14 +15519,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15536,14 +15536,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15560,7 +15560,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15570,14 +15570,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15587,14 +15587,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15604,14 +15604,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15628,7 +15628,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15638,14 +15638,14 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15655,14 +15655,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15679,7 +15679,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15689,14 +15689,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15713,7 +15713,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15730,7 +15730,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15764,7 +15764,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15781,7 +15781,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15791,14 +15791,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15832,7 +15832,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15883,7 +15883,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15893,14 +15893,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15917,7 +15917,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15927,14 +15927,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15944,14 +15944,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15968,7 +15968,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15978,14 +15978,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15995,14 +15995,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16012,14 +16012,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16029,14 +16029,14 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16046,14 +16046,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16063,14 +16063,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16080,14 +16080,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16104,7 +16104,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16114,14 +16114,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16131,14 +16131,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16148,14 +16148,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16172,7 +16172,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16182,14 +16182,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16206,7 +16206,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16216,14 +16216,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16233,14 +16233,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16257,7 +16257,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16301,14 +16301,14 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16342,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16352,14 +16352,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16376,7 +16376,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16386,14 +16386,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16410,7 +16410,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16427,7 +16427,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16444,7 +16444,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16454,14 +16454,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16471,14 +16471,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16495,7 +16495,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16505,14 +16505,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16522,14 +16522,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16546,7 +16546,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16563,7 +16563,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16573,14 +16573,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16590,14 +16590,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16614,7 +16614,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16631,7 +16631,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16648,7 +16648,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16665,7 +16665,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16682,7 +16682,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16699,7 +16699,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16709,14 +16709,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16733,7 +16733,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16743,14 +16743,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16760,14 +16760,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16784,7 +16784,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16801,7 +16801,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16818,7 +16818,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16828,14 +16828,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16845,14 +16845,14 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16869,7 +16869,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16903,7 +16903,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16920,7 +16920,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16937,7 +16937,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16947,14 +16947,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16971,7 +16971,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16981,14 +16981,14 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16998,14 +16998,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -17015,14 +17015,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -17032,14 +17032,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -17049,14 +17049,14 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -17066,14 +17066,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -17083,14 +17083,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -17107,7 +17107,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17124,7 +17124,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17141,7 +17141,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17151,14 +17151,14 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17175,7 +17175,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17192,7 +17192,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17209,7 +17209,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17219,14 +17219,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17243,7 +17243,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17253,14 +17253,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17270,14 +17270,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17311,7 +17311,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17328,7 +17328,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17338,14 +17338,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17355,14 +17355,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17379,7 +17379,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17396,7 +17396,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17413,7 +17413,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17423,14 +17423,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17447,7 +17447,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17457,14 +17457,14 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17481,7 +17481,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17498,7 +17498,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17515,7 +17515,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17532,7 +17532,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17542,14 +17542,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17559,14 +17559,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17583,7 +17583,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17600,7 +17600,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17617,7 +17617,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17634,7 +17634,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17644,14 +17644,14 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17661,14 +17661,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17678,14 +17678,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17702,7 +17702,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17719,7 +17719,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17736,7 +17736,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17753,7 +17753,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17770,7 +17770,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17804,7 +17804,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17814,14 +17814,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17855,7 +17855,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17865,14 +17865,14 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17882,14 +17882,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17906,7 +17906,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17916,14 +17916,14 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17933,14 +17933,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17950,14 +17950,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17967,14 +17967,14 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -18008,7 +18008,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -18018,14 +18018,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18035,14 +18035,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -18052,14 +18052,14 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18069,14 +18069,14 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18086,14 +18086,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -18110,7 +18110,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -18127,7 +18127,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -18137,14 +18137,14 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -18154,14 +18154,14 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18178,7 +18178,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18195,7 +18195,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18263,7 +18263,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18273,14 +18273,14 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18290,14 +18290,14 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18307,14 +18307,14 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18331,7 +18331,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18341,14 +18341,14 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18358,14 +18358,14 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18375,14 +18375,14 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18392,14 +18392,14 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18409,14 +18409,14 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18426,14 +18426,14 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18443,14 +18443,14 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18467,7 +18467,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18477,14 +18477,14 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18501,7 +18501,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -18535,7 +18535,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18545,14 +18545,14 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18569,7 +18569,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18579,14 +18579,14 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18596,14 +18596,14 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18620,7 +18620,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18692,78 +18692,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>